--- a/Invoice/COM1040624.xlsx
+++ b/Invoice/COM1040624.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\SEG\docs\Invoice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{CBFD9F12-F45C-4A47-A825-2015BD3FE9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{042B5108-39D5-B044-B3DE-FB6B6F7CD1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>COMMERCIAL INVOICE</t>
   </si>
@@ -553,31 +553,31 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1052,82 +1052,82 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46" t="s">
+      <c r="C6" s="48"/>
+      <c r="D6" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
       <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
       <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46" t="s">
+      <c r="C9" s="48"/>
+      <c r="D9" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
       <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
       <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1157,14 +1157,14 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="21">
         <f>SUM(G18:G18)</f>
-        <v>12568500</v>
+        <v>11907000</v>
       </c>
       <c r="C15" s="22">
         <v>1</v>
       </c>
       <c r="D15" s="22">
         <f>SUM(D18:D18)</f>
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="12"/>
@@ -1211,7 +1211,7 @@
         <v>9781613527962</v>
       </c>
       <c r="D18" s="40">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E18" s="28">
         <v>189000</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G18" s="42">
         <f t="shared" ref="G18" si="0">(E18*D18)-((E18*D18)*F18)</f>
-        <v>12568500</v>
+        <v>11907000</v>
       </c>
       <c r="H18" s="26"/>
     </row>
@@ -1233,8 +1233,8 @@
       <c r="F19" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
     </row>
     <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="29"/>
@@ -1312,15 +1312,15 @@
       <c r="H27" s="37"/>
     </row>
     <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="50"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="47"/>
     </row>
     <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E29" s="4"/>
@@ -1336,18 +1336,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D7:G8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:G9"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D10:G12"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D7:G8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:G9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" orientation="landscape"/>
